--- a/suppl/variant_filtering_metadata.xlsx
+++ b/suppl/variant_filtering_metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomparee/Documents/Documents - MacBook Pro de tom/rockmanlab/becei/RILs/suppl/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomparee/Documents/Documents - MacBook Pro de tom/rockmanlab/becei/CBCI_RILs/suppl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92887D54-2F9B-D848-968A-389F13B0B771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B3A0FD-B1A8-3248-A575-8173772508E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7980" yWindow="500" windowWidth="28040" windowHeight="16640" xr2:uid="{A8051D91-00D2-9048-AD11-4A7AF548091D}"/>
+    <workbookView xWindow="7400" yWindow="500" windowWidth="28040" windowHeight="16640" xr2:uid="{A8051D91-00D2-9048-AD11-4A7AF548091D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>stringent filtering</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>duplication?</t>
-  </si>
-  <si>
-    <t>NA is &gt;= founder</t>
   </si>
   <si>
     <t>fixed alt</t>
@@ -92,7 +89,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -107,6 +104,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Grande"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,10 +132,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC59E370-D01E-004C-93B9-2B8F30EE72B7}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -462,12 +466,12 @@
     <col min="10" max="10" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -479,7 +483,7 @@
         <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>11</v>
@@ -490,11 +494,9 @@
       <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -504,29 +506,28 @@
       <c r="C2" s="2">
         <v>76261</v>
       </c>
-      <c r="D2" s="2">
-        <v>381782</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D2" s="3">
+        <f>SUM(E2:I2)</f>
+        <v>361314</v>
+      </c>
+      <c r="E2" s="3">
         <v>244289</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>45658</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>7519</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>34681</v>
       </c>
-      <c r="I2" s="2">
-        <v>29335</v>
-      </c>
-      <c r="J2" s="2">
-        <v>42724</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I2" s="3">
+        <v>29167</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -536,29 +537,28 @@
       <c r="C3" s="2">
         <v>84710</v>
       </c>
-      <c r="D3" s="2">
-        <v>438622</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="3">
+        <f t="shared" ref="D3:D7" si="0">SUM(E3:I3)</f>
+        <v>400185</v>
+      </c>
+      <c r="E3" s="3">
         <v>273480</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>40215</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3">
         <v>9814</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3">
         <v>42935</v>
       </c>
-      <c r="I3" s="2">
-        <v>33995</v>
-      </c>
-      <c r="J3" s="2">
-        <v>69534</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I3" s="3">
+        <v>33741</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -568,29 +568,28 @@
       <c r="C4" s="2">
         <v>63491</v>
       </c>
-      <c r="D4" s="2">
-        <v>369505</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="D4" s="3">
+        <f t="shared" si="0"/>
+        <v>347559</v>
+      </c>
+      <c r="E4" s="3">
         <v>226134</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>48383</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>7655</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>34273</v>
       </c>
-      <c r="I4" s="2">
-        <v>31297</v>
-      </c>
-      <c r="J4" s="2">
-        <v>45008</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I4" s="3">
+        <v>31114</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -600,29 +599,28 @@
       <c r="C5" s="2">
         <v>83113</v>
       </c>
-      <c r="D5" s="2">
-        <v>399712</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" s="3">
+        <f t="shared" si="0"/>
+        <v>382969</v>
+      </c>
+      <c r="E5" s="3">
         <v>267153</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>41207</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>8404</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <v>39376</v>
       </c>
-      <c r="I5" s="2">
-        <v>26970</v>
-      </c>
-      <c r="J5" s="2">
-        <v>39241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I5" s="3">
+        <v>26829</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -632,29 +630,28 @@
       <c r="C6" s="2">
         <v>147778</v>
       </c>
-      <c r="D6" s="2">
-        <v>546030</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D6" s="3">
+        <f t="shared" si="0"/>
+        <v>527906</v>
+      </c>
+      <c r="E6" s="3">
         <v>386994</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>67485</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>11335</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>30404</v>
       </c>
-      <c r="I6" s="2">
-        <v>31889</v>
-      </c>
-      <c r="J6" s="2">
-        <v>36341</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I6" s="3">
+        <v>31688</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -664,29 +661,28 @@
       <c r="C7" s="2">
         <v>65785</v>
       </c>
-      <c r="D7" s="2">
-        <v>510161</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D7" s="3">
+        <f t="shared" si="0"/>
+        <v>423047</v>
+      </c>
+      <c r="E7" s="3">
         <v>159247</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>33340</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="3">
         <v>5573</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>165945</v>
       </c>
-      <c r="I7" s="2">
-        <v>59148</v>
-      </c>
-      <c r="J7" s="2">
-        <v>127460</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I7" s="3">
+        <v>58942</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -699,57 +695,54 @@
         <v>521138</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" ref="D8:E10" si="0">SUM(D2:D7)</f>
-        <v>2645812</v>
+        <f t="shared" ref="D8:I8" si="1">SUM(D2:D7)</f>
+        <v>2442980</v>
       </c>
       <c r="E8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1557297</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" ref="F8" si="1">SUM(F2:F7)</f>
+        <f t="shared" si="1"/>
         <v>276288</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" ref="G8" si="2">SUM(G2:G7)</f>
+        <f t="shared" si="1"/>
         <v>50300</v>
       </c>
       <c r="H8" s="2">
-        <f t="shared" ref="H8" si="3">SUM(H2:H7)</f>
+        <f t="shared" si="1"/>
         <v>347614</v>
       </c>
       <c r="I8" s="2">
-        <f t="shared" ref="I8" si="4">SUM(I2:I7)</f>
-        <v>212634</v>
-      </c>
-      <c r="J8" s="2">
-        <f t="shared" ref="J8" si="5">SUM(J2:J7)</f>
-        <v>360308</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D10" s="2">
-        <f>2645812-I8</f>
-        <v>2433178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D13" s="2">
-        <f>SUM(E13:H13)</f>
-        <v>2231499</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1557297</v>
-      </c>
-      <c r="F13" s="2">
-        <v>276288</v>
-      </c>
-      <c r="G13" s="2">
-        <v>50300</v>
-      </c>
-      <c r="H13" s="2">
-        <v>347614</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>211481</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J11" s="2">
+        <f>SUM(E8:I8)</f>
+        <v>2442980</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="K14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/suppl/variant_filtering_metadata.xlsx
+++ b/suppl/variant_filtering_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tomparee/Documents/Documents - MacBook Pro de tom/rockmanlab/becei/CBCI_RILs/suppl/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B3A0FD-B1A8-3248-A575-8173772508E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BCF838-EA73-2A41-8312-D8ACF6E12AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7400" yWindow="500" windowWidth="28040" windowHeight="16640" xr2:uid="{A8051D91-00D2-9048-AD11-4A7AF548091D}"/>
+    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16640" xr2:uid="{A8051D91-00D2-9048-AD11-4A7AF548091D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -724,10 +724,7 @@
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="J11" s="2">
-        <f>SUM(E8:I8)</f>
-        <v>2442980</v>
-      </c>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E12" s="2"/>
